--- a/salidas/empresas/SPG.xlsx
+++ b/salidas/empresas/SPG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>32.23006057739258</v>
+        <v>32.23006820678711</v>
       </c>
       <c r="C2" t="n">
         <v>76.88736724853516</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>32.58511734008789</v>
+        <v>32.58512115478516</v>
       </c>
       <c r="C3" t="n">
         <v>77.00803375244141</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>33.04460525512695</v>
+        <v>33.04462051391602</v>
       </c>
       <c r="C4" t="n">
         <v>78.09395599365234</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>32.15701675415039</v>
+        <v>32.15702056884766</v>
       </c>
       <c r="C5" t="n">
         <v>75.99635314941406</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.57181549072266</v>
+        <v>31.57182693481445</v>
       </c>
       <c r="C6" t="n">
         <v>73.90803527832031</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>32.88417434692383</v>
+        <v>32.88417816162109</v>
       </c>
       <c r="C7" t="n">
         <v>76.98018646240234</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>33.91107559204102</v>
+        <v>33.91104888916016</v>
       </c>
       <c r="C8" t="n">
         <v>79.38407897949219</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>33.92839813232422</v>
+        <v>33.92840576171875</v>
       </c>
       <c r="C9" t="n">
         <v>78.69725036621094</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>36.26124572753906</v>
+        <v>36.26126098632812</v>
       </c>
       <c r="C10" t="n">
         <v>84.10832214355469</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>38.85421371459961</v>
+        <v>38.85419845581055</v>
       </c>
       <c r="C11" t="n">
         <v>90.12268829345703</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>41.13554763793945</v>
+        <v>41.13555526733398</v>
       </c>
       <c r="C12" t="n">
         <v>94.65203094482422</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.85722732543945</v>
+        <v>40.85723495483398</v>
       </c>
       <c r="C13" t="n">
         <v>94.01161193847656</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>46.14136505126953</v>
+        <v>46.14137268066406</v>
       </c>
       <c r="C14" t="n">
         <v>106.1702880859375</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>45.80123901367188</v>
+        <v>45.8012580871582</v>
       </c>
       <c r="C15" t="n">
         <v>104.6388473510742</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>45.1959228515625</v>
+        <v>45.19589996337891</v>
       </c>
       <c r="C16" t="n">
         <v>103.2559127807617</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>46.8331298828125</v>
+        <v>46.8331413269043</v>
       </c>
       <c r="C17" t="n">
         <v>106.9963302612305</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>44.20114898681641</v>
+        <v>44.20113754272461</v>
       </c>
       <c r="C18" t="n">
         <v>100.2208862304688</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>38.08552551269531</v>
+        <v>38.08552932739258</v>
       </c>
       <c r="C19" t="n">
         <v>86.35443115234375</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>35.42068481445312</v>
+        <v>35.42068862915039</v>
       </c>
       <c r="C20" t="n">
         <v>80.31221771240234</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>39.22544479370117</v>
+        <v>39.22543334960938</v>
       </c>
       <c r="C21" t="n">
         <v>88.09934234619141</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>41.32474136352539</v>
+        <v>41.32473754882812</v>
       </c>
       <c r="C22" t="n">
         <v>92.81430816650391</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>43.11409759521484</v>
+        <v>43.11410522460938</v>
       </c>
       <c r="C23" t="n">
         <v>96.83316802978516</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>41.03200531005859</v>
+        <v>41.03200149536133</v>
       </c>
       <c r="C24" t="n">
         <v>91.37568664550781</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>36.20150756835938</v>
+        <v>36.20151519775391</v>
       </c>
       <c r="C25" t="n">
         <v>80.61850738525391</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>37.25179672241211</v>
+        <v>37.25180435180664</v>
       </c>
       <c r="C26" t="n">
         <v>82.95742797851562</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>39.13220977783203</v>
+        <v>39.13223266601562</v>
       </c>
       <c r="C28" t="n">
         <v>86.23377227783203</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>42.05945587158203</v>
+        <v>42.05944061279297</v>
       </c>
       <c r="C29" t="n">
         <v>92.68436431884766</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>42.22587585449219</v>
+        <v>42.22591018676758</v>
       </c>
       <c r="C30" t="n">
         <v>92.22029876708984</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>39.36576080322266</v>
+        <v>39.36577224731445</v>
       </c>
       <c r="C32" t="n">
         <v>85.97389221191406</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>40.69620895385742</v>
+        <v>40.69623184204102</v>
       </c>
       <c r="C33" t="n">
         <v>88.06221771240234</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>41.60552215576172</v>
+        <v>41.60553741455078</v>
       </c>
       <c r="C34" t="n">
         <v>90.02987670898438</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.7507152557373</v>
+        <v>28.75070381164551</v>
       </c>
       <c r="C35" t="n">
         <v>62.21342849731445</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.69196510314941</v>
+        <v>20.69196128845215</v>
       </c>
       <c r="C36" t="n">
         <v>44.08679580688477</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>23.14450645446777</v>
+        <v>23.14450836181641</v>
       </c>
       <c r="C37" t="n">
         <v>49.31224060058594</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>18.72295761108398</v>
+        <v>18.72296333312988</v>
       </c>
       <c r="C38" t="n">
         <v>39.8915901184082</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.70138931274414</v>
+        <v>14.70139503479004</v>
       </c>
       <c r="C39" t="n">
         <v>30.72153472900391</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.38538360595703</v>
+        <v>15.3853816986084</v>
       </c>
       <c r="C40" t="n">
         <v>32.15087509155273</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>22.91816711425781</v>
+        <v>22.91817665100098</v>
       </c>
       <c r="C41" t="n">
         <v>47.89218139648438</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>23.10941886901855</v>
+        <v>23.10940933227539</v>
       </c>
       <c r="C43" t="n">
         <v>47.73439788818359</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>25.03708267211914</v>
+        <v>25.03707504272461</v>
       </c>
       <c r="C44" t="n">
         <v>51.71612930297852</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>28.8480339050293</v>
+        <v>28.84803009033203</v>
       </c>
       <c r="C45" t="n">
         <v>59.47479248046875</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>31.48253631591797</v>
+        <v>31.48254203796387</v>
       </c>
       <c r="C46" t="n">
         <v>64.90623474121094</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>30.78423881530762</v>
+        <v>30.78423118591309</v>
       </c>
       <c r="C47" t="n">
         <v>63.46657562255859</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>33.20992660522461</v>
+        <v>33.20993041992188</v>
       </c>
       <c r="C48" t="n">
         <v>68.35371398925781</v>
@@ -1393,7 +1405,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>32.90825653076172</v>
+        <v>32.90826416015625</v>
       </c>
       <c r="C50" t="n">
         <v>67.73283386230469</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>36.09133529663086</v>
+        <v>36.09133148193359</v>
       </c>
       <c r="C51" t="n">
         <v>73.65004730224609</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>38.6775016784668</v>
+        <v>38.67750549316406</v>
       </c>
       <c r="C52" t="n">
         <v>78.92756652832031</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>41.03781509399414</v>
+        <v>41.03780364990234</v>
       </c>
       <c r="C53" t="n">
         <v>83.74411773681641</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>39.45971298217773</v>
+        <v>39.45969772338867</v>
       </c>
       <c r="C54" t="n">
         <v>79.99059295654297</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.47349548339844</v>
+        <v>37.47348785400391</v>
       </c>
       <c r="C55" t="n">
         <v>75.96424865722656</v>
@@ -1562,11 +1574,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>41.40415954589844</v>
+        <v>41.40415573120117</v>
       </c>
       <c r="C56" t="n">
         <v>83.93226623535156</v>
@@ -1581,11 +1593,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>42.25784301757812</v>
+        <v>42.25783920288086</v>
       </c>
       <c r="C57" t="n">
         <v>85.08937072753906</v>
@@ -1606,11 +1618,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>43.32771301269531</v>
+        <v>43.32771682739258</v>
       </c>
       <c r="C58" t="n">
         <v>87.24365234375</v>
@@ -1631,11 +1643,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>44.86011505126953</v>
+        <v>44.86011123657227</v>
       </c>
       <c r="C59" t="n">
         <v>90.32925415039062</v>
@@ -1656,11 +1668,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>46.38448333740234</v>
+        <v>46.3845100402832</v>
       </c>
       <c r="C60" t="n">
         <v>92.66227722167969</v>
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>46.85071563720703</v>
+        <v>46.85070419311523</v>
       </c>
       <c r="C61" t="n">
         <v>93.59360504150391</v>
@@ -1706,11 +1718,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>47.77367782592773</v>
+        <v>47.77366256713867</v>
       </c>
       <c r="C62" t="n">
         <v>95.43743896484375</v>
@@ -1731,11 +1743,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>52.21186065673828</v>
+        <v>52.21187591552734</v>
       </c>
       <c r="C63" t="n">
         <v>103.5183410644531</v>
@@ -1760,11 +1772,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>50.84536361694336</v>
+        <v>50.84537887573242</v>
       </c>
       <c r="C64" t="n">
         <v>100.8090286254883</v>
@@ -1789,7 +1801,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1818,11 +1830,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>56.40304946899414</v>
+        <v>56.40302276611328</v>
       </c>
       <c r="C66" t="n">
         <v>111.0630264282227</v>
@@ -1847,11 +1859,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>55.52874374389648</v>
+        <v>55.52872467041016</v>
       </c>
       <c r="C67" t="n">
         <v>109.3414840698242</v>
@@ -1876,11 +1888,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>57.57352447509766</v>
+        <v>57.57350158691406</v>
       </c>
       <c r="C68" t="n">
         <v>113.3678283691406</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>56.53129959106445</v>
+        <v>56.53128814697266</v>
       </c>
       <c r="C69" t="n">
         <v>110.5362167358398</v>
@@ -1934,11 +1946,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>52.91330337524414</v>
+        <v>52.91329956054688</v>
       </c>
       <c r="C70" t="n">
         <v>103.4618988037109</v>
@@ -1963,11 +1975,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>61.79471588134766</v>
+        <v>61.79473114013672</v>
       </c>
       <c r="C71" t="n">
         <v>120.8278427124023</v>
@@ -1992,11 +2004,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>60.24583435058594</v>
+        <v>60.24585723876953</v>
       </c>
       <c r="C72" t="n">
         <v>116.9708404541016</v>
@@ -2021,11 +2033,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>62.57847213745117</v>
+        <v>62.57849502563477</v>
       </c>
       <c r="C73" t="n">
         <v>121.298210144043</v>
@@ -2050,11 +2062,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>65.93699645996094</v>
+        <v>65.93698120117188</v>
       </c>
       <c r="C74" t="n">
         <v>127.8080902099609</v>
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>66.21248626708984</v>
+        <v>66.21250152587891</v>
       </c>
       <c r="C75" t="n">
         <v>127.4506072998047</v>
@@ -2108,11 +2120,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>71.19750213623047</v>
+        <v>71.19746398925781</v>
       </c>
       <c r="C76" t="n">
         <v>137.0460968017578</v>
@@ -2137,7 +2149,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2166,11 +2178,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>72.56655883789062</v>
+        <v>72.5665283203125</v>
       </c>
       <c r="C78" t="n">
         <v>138.7770385742188</v>
@@ -2195,11 +2207,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>76.57069396972656</v>
+        <v>76.57072448730469</v>
       </c>
       <c r="C79" t="n">
         <v>146.4346160888672</v>
@@ -2224,11 +2236,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>78.94663238525391</v>
+        <v>78.94662475585938</v>
       </c>
       <c r="C80" t="n">
         <v>150.9783630371094</v>
@@ -2253,11 +2265,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>78.58985900878906</v>
+        <v>78.58986663818359</v>
       </c>
       <c r="C81" t="n">
         <v>149.2944488525391</v>
@@ -2282,11 +2294,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>75.17787933349609</v>
+        <v>75.17790985107422</v>
       </c>
       <c r="C82" t="n">
         <v>142.8127899169922</v>
@@ -2311,7 +2323,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2340,11 +2352,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>75.88621520996094</v>
+        <v>75.88619995117188</v>
       </c>
       <c r="C84" t="n">
         <v>143.1138305664062</v>
@@ -2369,11 +2381,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>78.85919189453125</v>
+        <v>78.85918426513672</v>
       </c>
       <c r="C85" t="n">
         <v>148.7205963134766</v>
@@ -2398,11 +2410,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>79.90174865722656</v>
+        <v>79.90175628662109</v>
       </c>
       <c r="C86" t="n">
         <v>150.6867370605469</v>
@@ -2427,11 +2439,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>79.80461883544922</v>
+        <v>79.80461120605469</v>
       </c>
       <c r="C87" t="n">
         <v>149.4449615478516</v>
@@ -2456,7 +2468,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2485,11 +2497,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>89.45492553710938</v>
+        <v>89.45487213134766</v>
       </c>
       <c r="C89" t="n">
         <v>167.5164642333984</v>
@@ -2514,11 +2526,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>84.15245819091797</v>
+        <v>84.15244293212891</v>
       </c>
       <c r="C90" t="n">
         <v>156.5757293701172</v>
@@ -2543,11 +2555,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>79.84471893310547</v>
+        <v>79.84471130371094</v>
       </c>
       <c r="C91" t="n">
         <v>148.5606842041016</v>
@@ -2572,11 +2584,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>80.92671966552734</v>
+        <v>80.92669677734375</v>
       </c>
       <c r="C92" t="n">
         <v>150.5738525390625</v>
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>74.18051147460938</v>
+        <v>74.18053436279297</v>
       </c>
       <c r="C93" t="n">
         <v>136.9990539550781</v>
@@ -2630,11 +2642,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>75.50489807128906</v>
+        <v>75.5048828125</v>
       </c>
       <c r="C94" t="n">
         <v>139.4449615478516</v>
@@ -2659,11 +2671,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>78.72415924072266</v>
+        <v>78.72417449951172</v>
       </c>
       <c r="C95" t="n">
         <v>145.3904113769531</v>
@@ -2688,11 +2700,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>76.94648742675781</v>
+        <v>76.94651031494141</v>
       </c>
       <c r="C96" t="n">
         <v>140.9689636230469</v>
@@ -2717,11 +2729,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>78.13265228271484</v>
+        <v>78.13265991210938</v>
       </c>
       <c r="C97" t="n">
         <v>143.1420440673828</v>
@@ -2746,11 +2758,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>79.50879669189453</v>
+        <v>79.5087890625</v>
       </c>
       <c r="C98" t="n">
         <v>145.6632232666016</v>
@@ -2775,7 +2787,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>84.87883758544922</v>
+        <v>84.87881469726562</v>
       </c>
       <c r="C100" t="n">
         <v>154.2803344726562</v>
@@ -2833,11 +2845,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>89.64031982421875</v>
+        <v>89.64034271240234</v>
       </c>
       <c r="C101" t="n">
         <v>162.9350891113281</v>
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>92.2666015625</v>
+        <v>92.26658630371094</v>
       </c>
       <c r="C102" t="n">
         <v>166.4600067138672</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>92.16683959960938</v>
+        <v>92.16686248779297</v>
       </c>
       <c r="C103" t="n">
         <v>166.2799987792969</v>
@@ -2920,11 +2932,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>93.22548675537109</v>
+        <v>93.22550964355469</v>
       </c>
       <c r="C104" t="n">
         <v>168.1900024414062</v>
@@ -2949,7 +2961,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2978,11 +2990,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>91.85030364990234</v>
+        <v>91.85029602050781</v>
       </c>
       <c r="C106" t="n">
         <v>164.4199981689453</v>
@@ -3007,11 +3019,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>100.1124801635742</v>
+        <v>100.1124649047852</v>
       </c>
       <c r="C107" t="n">
         <v>179.2100067138672</v>
@@ -3036,11 +3048,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>101.7329406738281</v>
+        <v>101.7329254150391</v>
       </c>
       <c r="C108" t="n">
         <v>180.8000030517578</v>
@@ -3065,11 +3077,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>102.4700393676758</v>
+        <v>102.4700622558594</v>
       </c>
       <c r="C109" t="n">
         <v>182.1100006103516</v>
@@ -3094,11 +3106,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>111.7824554443359</v>
+        <v>111.7824172973633</v>
       </c>
       <c r="C110" t="n">
         <v>198.6600036621094</v>
@@ -3123,11 +3135,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>107.8877563476562</v>
+        <v>107.8877716064453</v>
       </c>
       <c r="C111" t="n">
         <v>190.3600006103516</v>
@@ -3152,11 +3164,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>110.8802185058594</v>
+        <v>110.8802337646484</v>
       </c>
       <c r="C112" t="n">
         <v>195.6399993896484</v>
@@ -3181,11 +3193,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>102.8606262207031</v>
+        <v>102.8606491088867</v>
       </c>
       <c r="C113" t="n">
         <v>181.4900054931641</v>
@@ -3210,11 +3222,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>103.6526412963867</v>
+        <v>103.6526565551758</v>
       </c>
       <c r="C114" t="n">
         <v>181.3999938964844</v>
@@ -3239,11 +3251,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>98.86431121826172</v>
+        <v>98.86428070068359</v>
       </c>
       <c r="C115" t="n">
         <v>173.0200042724609</v>
@@ -3268,11 +3280,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>106.9782104492188</v>
+        <v>106.9782485961914</v>
       </c>
       <c r="C116" t="n">
         <v>187.2200012207031</v>
@@ -3297,11 +3309,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>103.2979431152344</v>
+        <v>103.297966003418</v>
       </c>
       <c r="C117" t="n">
         <v>179.3200073242188</v>
@@ -3326,11 +3338,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>105.8325805664062</v>
+        <v>105.8326110839844</v>
       </c>
       <c r="C118" t="n">
         <v>183.7200012207031</v>
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>116.0517959594727</v>
+        <v>116.0518112182617</v>
       </c>
       <c r="C119" t="n">
         <v>201.4600067138672</v>
@@ -3384,11 +3396,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>108.1784591674805</v>
+        <v>108.178466796875</v>
       </c>
       <c r="C120" t="n">
         <v>186.2400054931641</v>
@@ -3413,11 +3425,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>112.9415130615234</v>
+        <v>112.9414901733398</v>
       </c>
       <c r="C121" t="n">
         <v>194.4400024414062</v>
@@ -3442,11 +3454,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>108.2017211914062</v>
+        <v>108.2016677856445</v>
       </c>
       <c r="C122" t="n">
         <v>186.2799987792969</v>
@@ -3471,11 +3483,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>111.1999893188477</v>
+        <v>111.2000198364258</v>
       </c>
       <c r="C123" t="n">
         <v>189.7299957275391</v>
@@ -3500,11 +3512,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>121.7263336181641</v>
+        <v>121.7262878417969</v>
       </c>
       <c r="C124" t="n">
         <v>207.6900024414062</v>
@@ -3529,11 +3541,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>117.9049377441406</v>
+        <v>117.904914855957</v>
       </c>
       <c r="C125" t="n">
         <v>201.1699981689453</v>
@@ -3558,11 +3570,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>116.7515563964844</v>
+        <v>116.7515106201172</v>
       </c>
       <c r="C126" t="n">
         <v>197.6399993896484</v>
@@ -3587,7 +3599,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3616,11 +3628,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>134.1189270019531</v>
+        <v>134.1189727783203</v>
       </c>
       <c r="C128" t="n">
         <v>227.0399932861328</v>
@@ -3645,7 +3657,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3674,11 +3686,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>123.2314147949219</v>
+        <v>123.2314376831055</v>
       </c>
       <c r="C130" t="n">
         <v>207.0099945068359</v>
@@ -3703,11 +3715,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>110.700569152832</v>
+        <v>110.7005386352539</v>
       </c>
       <c r="C131" t="n">
         <v>185.9600067138672</v>
@@ -3732,11 +3744,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>107.9193420410156</v>
+        <v>107.9193344116211</v>
       </c>
       <c r="C132" t="n">
         <v>179.6499938964844</v>
@@ -3761,11 +3773,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>106.7299575805664</v>
+        <v>106.7299118041992</v>
       </c>
       <c r="C133" t="n">
         <v>177.6699981689453</v>
@@ -3790,11 +3802,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>110.3943176269531</v>
+        <v>110.3943557739258</v>
       </c>
       <c r="C134" t="n">
         <v>183.7700042724609</v>
@@ -3819,11 +3831,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>111.848274230957</v>
+        <v>111.8482971191406</v>
       </c>
       <c r="C135" t="n">
         <v>184.3999938964844</v>
@@ -3848,11 +3860,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>104.3452529907227</v>
+        <v>104.3452377319336</v>
       </c>
       <c r="C136" t="n">
         <v>172.0299987792969</v>
@@ -3877,11 +3889,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>100.2388763427734</v>
+        <v>100.2388687133789</v>
       </c>
       <c r="C137" t="n">
         <v>165.2599945068359</v>
@@ -3906,11 +3918,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>94.61214447021484</v>
+        <v>94.61209106445312</v>
       </c>
       <c r="C138" t="n">
         <v>154.25</v>
@@ -3935,11 +3947,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>99.21852111816406</v>
+        <v>99.21852874755859</v>
       </c>
       <c r="C139" t="n">
         <v>161.7599945068359</v>
@@ -3964,11 +3976,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>97.21896362304688</v>
+        <v>97.21892547607422</v>
       </c>
       <c r="C140" t="n">
         <v>158.5</v>
@@ -3993,11 +4005,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>97.29918670654297</v>
+        <v>97.29921722412109</v>
       </c>
       <c r="C141" t="n">
         <v>156.8500061035156</v>
@@ -4022,11 +4034,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>99.87974548339844</v>
+        <v>99.87977600097656</v>
       </c>
       <c r="C142" t="n">
         <v>161.0099945068359</v>
@@ -4051,11 +4063,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>96.35626220703125</v>
+        <v>96.35626983642578</v>
       </c>
       <c r="C143" t="n">
         <v>155.3300018310547</v>
@@ -4080,11 +4092,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>101.5087585449219</v>
+        <v>101.5087356567383</v>
       </c>
       <c r="C144" t="n">
         <v>161.75</v>
@@ -4109,11 +4121,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>107.7781829833984</v>
+        <v>107.7781448364258</v>
       </c>
       <c r="C145" t="n">
         <v>171.7400054931641</v>
@@ -4138,7 +4150,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4167,11 +4179,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>97.55079650878906</v>
+        <v>97.55076599121094</v>
       </c>
       <c r="C147" t="n">
         <v>153.5099945068359</v>
@@ -4196,11 +4208,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>98.08458709716797</v>
+        <v>98.08460235595703</v>
       </c>
       <c r="C148" t="n">
         <v>154.3500061035156</v>
@@ -4225,11 +4237,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>99.34916687011719</v>
+        <v>99.34915924072266</v>
       </c>
       <c r="C149" t="n">
         <v>156.3399963378906</v>
@@ -4254,11 +4266,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>103.1149520874023</v>
+        <v>103.1149673461914</v>
       </c>
       <c r="C150" t="n">
         <v>160.2200012207031</v>
@@ -4283,11 +4295,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>109.5315170288086</v>
+        <v>109.5315246582031</v>
       </c>
       <c r="C151" t="n">
         <v>170.1900024414062</v>
@@ -4312,7 +4324,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4341,11 +4353,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>119.1402435302734</v>
+        <v>119.1402587890625</v>
       </c>
       <c r="C153" t="n">
         <v>183.0299987792969</v>
@@ -4370,11 +4382,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>115.0523834228516</v>
+        <v>115.0524063110352</v>
       </c>
       <c r="C154" t="n">
         <v>176.75</v>
@@ -4399,7 +4411,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4428,11 +4440,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>122.175666809082</v>
+        <v>122.1756591796875</v>
       </c>
       <c r="C156" t="n">
         <v>185.6900024414062</v>
@@ -4457,11 +4469,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>110.5298614501953</v>
+        <v>110.5298385620117</v>
       </c>
       <c r="C157" t="n">
         <v>167.9900054931641</v>
@@ -4486,11 +4498,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>119.8267669677734</v>
+        <v>119.8267211914062</v>
       </c>
       <c r="C158" t="n">
         <v>182.1199951171875</v>
@@ -4515,7 +4527,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4544,11 +4556,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>121.232292175293</v>
+        <v>121.2322692871094</v>
       </c>
       <c r="C160" t="n">
         <v>182.2100067138672</v>
@@ -4573,11 +4585,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>115.570198059082</v>
+        <v>115.5701675415039</v>
       </c>
       <c r="C161" t="n">
         <v>173.6999969482422</v>
@@ -4602,11 +4614,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>109.1092529296875</v>
+        <v>109.1092224121094</v>
       </c>
       <c r="C162" t="n">
         <v>162.0899963378906</v>
@@ -4631,7 +4643,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4660,11 +4672,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>109.1832580566406</v>
+        <v>109.1832809448242</v>
       </c>
       <c r="C164" t="n">
         <v>162.1999969482422</v>
@@ -4689,11 +4701,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>101.660888671875</v>
+        <v>101.6608810424805</v>
       </c>
       <c r="C165" t="n">
         <v>148.9400024414062</v>
@@ -4718,11 +4730,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>106.2408447265625</v>
+        <v>106.240852355957</v>
       </c>
       <c r="C166" t="n">
         <v>155.6499938964844</v>
@@ -4747,11 +4759,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>102.8485107421875</v>
+        <v>102.8485412597656</v>
       </c>
       <c r="C167" t="n">
         <v>150.6799926757812</v>
@@ -4776,11 +4788,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>104.6340026855469</v>
+        <v>104.6339721679688</v>
       </c>
       <c r="C168" t="n">
         <v>151.2100067138672</v>
@@ -4805,11 +4817,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>103.0770263671875</v>
+        <v>103.0770111083984</v>
       </c>
       <c r="C169" t="n">
         <v>148.9600067138672</v>
@@ -4834,11 +4846,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>92.1368408203125</v>
+        <v>92.13682556152344</v>
       </c>
       <c r="C170" t="n">
         <v>133.1499938964844</v>
@@ -4863,11 +4875,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>86.47348022460938</v>
+        <v>86.47345733642578</v>
       </c>
       <c r="C171" t="n">
         <v>123.0800018310547</v>
@@ -4892,11 +4904,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>38.54350280761719</v>
+        <v>38.54351043701172</v>
       </c>
       <c r="C172" t="n">
         <v>54.86000061035156</v>
@@ -4921,11 +4933,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>46.91121292114258</v>
+        <v>46.91122055053711</v>
       </c>
       <c r="C173" t="n">
         <v>66.76999664306641</v>
@@ -4950,7 +4962,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4979,7 +4991,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5008,11 +5020,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>44.68996047973633</v>
+        <v>44.68996429443359</v>
       </c>
       <c r="C176" t="n">
         <v>62.34999847412109</v>
@@ -5037,11 +5049,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>48.63214111328125</v>
+        <v>48.63214492797852</v>
       </c>
       <c r="C177" t="n">
         <v>67.84999847412109</v>
@@ -5066,11 +5078,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>46.36001968383789</v>
+        <v>46.36001586914062</v>
       </c>
       <c r="C178" t="n">
         <v>64.68000030517578</v>
@@ -5091,11 +5103,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>45.85899353027344</v>
+        <v>45.8589973449707</v>
       </c>
       <c r="C179" t="n">
         <v>62.81000137329102</v>
@@ -5116,11 +5128,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>60.28623199462891</v>
+        <v>60.28620910644531</v>
       </c>
       <c r="C180" t="n">
         <v>82.56999969482422</v>
@@ -5141,11 +5153,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>63.2469482421875</v>
+        <v>63.24695205688477</v>
       </c>
       <c r="C181" t="n">
         <v>85.27999877929688</v>
@@ -5166,11 +5178,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>68.92048645019531</v>
+        <v>68.92046356201172</v>
       </c>
       <c r="C182" t="n">
         <v>92.93000030517578</v>
@@ -5191,11 +5203,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>83.74584197998047</v>
+        <v>83.74583435058594</v>
       </c>
       <c r="C183" t="n">
         <v>112.9199981689453</v>
@@ -5216,11 +5228,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>84.37622833251953</v>
+        <v>84.376220703125</v>
       </c>
       <c r="C184" t="n">
         <v>113.7699966430664</v>
@@ -5241,11 +5253,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>91.30145263671875</v>
+        <v>91.30146026611328</v>
       </c>
       <c r="C185" t="n">
         <v>121.7399978637695</v>
@@ -5266,11 +5278,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>96.36378479003906</v>
+        <v>96.36377716064453</v>
       </c>
       <c r="C186" t="n">
         <v>128.4900054931641</v>
@@ -5291,7 +5303,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5316,11 +5328,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>95.91546630859375</v>
+        <v>95.91545104980469</v>
       </c>
       <c r="C188" t="n">
         <v>126.5199966430664</v>
@@ -5341,11 +5353,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>101.9272384643555</v>
+        <v>101.9272232055664</v>
       </c>
       <c r="C189" t="n">
         <v>134.4499969482422</v>
@@ -5366,11 +5378,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>99.64150238037109</v>
+        <v>99.64148712158203</v>
       </c>
       <c r="C190" t="n">
         <v>129.9700012207031</v>
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>112.3755645751953</v>
+        <v>112.3755569458008</v>
       </c>
       <c r="C191" t="n">
         <v>146.5800018310547</v>
@@ -5416,11 +5428,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>117.1747970581055</v>
+        <v>117.1747817993164</v>
       </c>
       <c r="C192" t="n">
         <v>152.8399963378906</v>
@@ -5441,11 +5453,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>123.7848587036133</v>
+        <v>123.7848663330078</v>
       </c>
       <c r="C193" t="n">
         <v>159.7700042724609</v>
@@ -5466,11 +5478,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>114.046028137207</v>
+        <v>114.0460205078125</v>
       </c>
       <c r="C194" t="n">
         <v>147.1999969482422</v>
@@ -5491,11 +5503,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>106.5772705078125</v>
+        <v>106.5772247314453</v>
       </c>
       <c r="C195" t="n">
         <v>137.5599975585938</v>
@@ -5520,11 +5532,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>103.2249526977539</v>
+        <v>103.2249298095703</v>
       </c>
       <c r="C196" t="n">
         <v>131.5599975585938</v>
@@ -5549,11 +5561,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>92.58546447753906</v>
+        <v>92.58544921875</v>
       </c>
       <c r="C197" t="n">
         <v>118</v>
@@ -5578,11 +5590,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>89.95697784423828</v>
+        <v>89.95699310302734</v>
       </c>
       <c r="C198" t="n">
         <v>114.6500015258789</v>
@@ -5607,7 +5619,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5636,11 +5648,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>86.55182647705078</v>
+        <v>86.55186462402344</v>
       </c>
       <c r="C200" t="n">
         <v>108.6399993896484</v>
@@ -5665,11 +5677,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>81.24593353271484</v>
+        <v>81.24594116210938</v>
       </c>
       <c r="C201" t="n">
         <v>101.9800033569336</v>
@@ -5694,11 +5706,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>72.73274230957031</v>
+        <v>72.73271942138672</v>
       </c>
       <c r="C202" t="n">
         <v>89.75</v>
@@ -5723,11 +5735,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>88.31658935546875</v>
+        <v>88.31656646728516</v>
       </c>
       <c r="C203" t="n">
         <v>108.9800033569336</v>
@@ -5752,11 +5764,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>96.79328918457031</v>
+        <v>96.79328155517578</v>
       </c>
       <c r="C204" t="n">
         <v>119.4400024414062</v>
@@ -5781,11 +5793,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>96.66647338867188</v>
+        <v>96.66648101806641</v>
       </c>
       <c r="C205" t="n">
         <v>117.4800033569336</v>
@@ -5810,11 +5822,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>105.7012023925781</v>
+        <v>105.7011947631836</v>
       </c>
       <c r="C206" t="n">
         <v>128.4600067138672</v>
@@ -5839,11 +5851,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>100.4597320556641</v>
+        <v>100.4597396850586</v>
       </c>
       <c r="C207" t="n">
         <v>122.0899963378906</v>
@@ -5868,7 +5880,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5897,11 +5909,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>94.63771057128906</v>
+        <v>94.63773345947266</v>
       </c>
       <c r="C209" t="n">
         <v>113.3199996948242</v>
@@ -5926,11 +5938,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>87.81465148925781</v>
+        <v>87.81467437744141</v>
       </c>
       <c r="C210" t="n">
         <v>105.1500015258789</v>
@@ -5955,11 +5967,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>98.0511474609375</v>
+        <v>98.05115509033203</v>
       </c>
       <c r="C211" t="n">
         <v>115.4800033569336</v>
@@ -5984,7 +5996,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6013,7 +6025,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6042,11 +6054,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>93.25631713867188</v>
+        <v>93.25633239746094</v>
       </c>
       <c r="C214" t="n">
         <v>108.0299987792969</v>
@@ -6071,11 +6083,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>94.86195373535156</v>
+        <v>94.86196136474609</v>
       </c>
       <c r="C215" t="n">
         <v>109.8899993896484</v>
@@ -6100,11 +6112,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>107.8106307983398</v>
+        <v>107.8106231689453</v>
       </c>
       <c r="C216" t="n">
         <v>124.8899993896484</v>
@@ -6129,11 +6141,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>124.9352035522461</v>
+        <v>124.9352111816406</v>
       </c>
       <c r="C217" t="n">
         <v>142.6399993896484</v>
@@ -6158,11 +6170,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>121.4054260253906</v>
+        <v>121.4054489135742</v>
       </c>
       <c r="C218" t="n">
         <v>138.6100006103516</v>
@@ -6187,11 +6199,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>129.7525634765625</v>
+        <v>129.7525177001953</v>
       </c>
       <c r="C219" t="n">
         <v>148.1399993896484</v>
@@ -6216,11 +6228,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>138.8436279296875</v>
+        <v>138.8435974121094</v>
       </c>
       <c r="C220" t="n">
         <v>156.4900054931641</v>
@@ -6245,11 +6257,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>124.6833267211914</v>
+        <v>124.6833038330078</v>
       </c>
       <c r="C221" t="n">
         <v>140.5299987792969</v>
@@ -6274,7 +6286,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6303,7 +6315,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6332,11 +6344,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>137.9314270019531</v>
+        <v>137.9314117431641</v>
       </c>
       <c r="C224" t="n">
         <v>153.4400024414062</v>
@@ -6361,11 +6373,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>150.4354858398438</v>
+        <v>150.4355010986328</v>
       </c>
       <c r="C225" t="n">
         <v>167.3500061035156</v>
@@ -6390,11 +6402,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>153.8540344238281</v>
+        <v>153.8540496826172</v>
       </c>
       <c r="C226" t="n">
         <v>169.0200042724609</v>
@@ -6419,7 +6431,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6448,11 +6460,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>167.1258087158203</v>
+        <v>167.1257781982422</v>
       </c>
       <c r="C228" t="n">
         <v>183.6000061035156</v>
@@ -6477,7 +6489,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6506,7 +6518,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6535,7 +6547,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6564,11 +6576,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>154.8249359130859</v>
+        <v>154.824951171875</v>
       </c>
       <c r="C232" t="n">
         <v>166.0800018310547</v>
@@ -6593,7 +6605,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6622,7 +6634,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6651,11 +6663,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>151.8324584960938</v>
+        <v>151.8324432373047</v>
       </c>
       <c r="C235" t="n">
         <v>160.7599945068359</v>
@@ -6680,11 +6692,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>154.6941833496094</v>
+        <v>154.6941986083984</v>
       </c>
       <c r="C236" t="n">
         <v>163.7899932861328</v>
@@ -6709,11 +6721,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>170.6273498535156</v>
+        <v>170.6273345947266</v>
       </c>
       <c r="C237" t="n">
         <v>180.6600036621094</v>
@@ -6738,7 +6750,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6767,11 +6779,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>167.9778289794922</v>
+        <v>167.9778137207031</v>
       </c>
       <c r="C239" t="n">
         <v>175.7599945068359</v>
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6825,11 +6837,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>179.0900115966797</v>
+        <v>179.0900268554688</v>
       </c>
       <c r="C241" t="n">
         <v>185.1100006103516</v>
@@ -6854,7 +6866,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6883,11 +6895,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>197.2205963134766</v>
+        <v>197.2205810546875</v>
       </c>
       <c r="C243" t="n">
         <v>203.8500061035156</v>
@@ -6912,11 +6924,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>182.5465240478516</v>
+        <v>182.5465087890625</v>
       </c>
       <c r="C244" t="n">
         <v>186.5299987792969</v>
@@ -6941,7 +6953,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6970,11 +6982,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>200.5339965820312</v>
+        <v>200.5340118408203</v>
       </c>
       <c r="C246" t="n">
         <v>204.9100036621094</v>
@@ -6999,7 +7011,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7028,7 +7040,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7057,7 +7069,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7086,32 +7098,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>204.1600036621094</v>
+        <v>204.6999969482422</v>
       </c>
       <c r="C250" t="n">
-        <v>204.1600036621094</v>
+        <v>204.6999969482422</v>
       </c>
       <c r="D250" t="n">
-        <v>20857900</v>
+        <v>21727600</v>
       </c>
       <c r="E250" t="n">
         <v>14.18</v>
       </c>
       <c r="F250" t="n">
-        <v>14.3977435586819</v>
+        <v>14.43582489056715</v>
       </c>
       <c r="G250" t="n">
         <v>324018022</v>
       </c>
       <c r="H250" t="n">
-        <v>66151520558.10944</v>
+        <v>66326488114.57547</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06437265393836643</v>
+        <v>0.06705676389815132</v>
       </c>
     </row>
   </sheetData>
@@ -7143,75 +7155,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40060</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7247,13 +7259,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7289,13 +7301,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7331,13 +7343,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40060</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7373,13 +7385,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7415,13 +7427,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7448,7 +7460,7 @@
       <c r="I7" t="n">
         <v>1.004818280767197</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7461,13 +7473,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7494,7 +7506,7 @@
       <c r="I8" t="n">
         <v>0.6097100963833775</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I9" t="n">
         <v>1.173679198285047</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I10" t="n">
         <v>1.561618062088429</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I11" t="n">
         <v>1.956726246472249</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I12" t="n">
         <v>2.502351834430856</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K12" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I13" t="n">
         <v>2.671683913452493</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I14" t="n">
         <v>2.803386641580433</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K14" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I15" t="n">
         <v>3.273753527751647</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K15" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I16" t="n">
         <v>4.750705550329258</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K16" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I17" t="n">
         <v>4.760112888052682</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K17" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I18" t="n">
         <v>4.675446848541863</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K18" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I19" t="n">
         <v>4.459078080903105</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I20" t="n">
         <v>3.264346190028222</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K20" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I21" t="n">
         <v>3.631232361241769</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K21" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I22" t="n">
         <v>3.781749764816557</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K22" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I23" t="n">
         <v>3.988711194731891</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K23" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I24" t="n">
         <v>4.167450611476952</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K24" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I25" t="n">
         <v>4.442643461900283</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="K25" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I26" t="n">
         <v>4.311909689557855</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K26" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I27" t="n">
         <v>4.45480714957667</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K27" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I28" t="n">
         <v>4.58</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K28" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I29" t="n">
         <v>4.79</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K29" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I30" t="n">
         <v>5.34</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K30" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I31" t="n">
         <v>5.31</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K31" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I32" t="n">
         <v>5.7</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K32" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I33" t="n">
         <v>5.63</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K33" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I34" t="n">
         <v>5.88</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K34" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I35" t="n">
         <v>5.87</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K35" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I36" t="n">
         <v>5.850000000000001</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K36" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I37" t="n">
         <v>5.63</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K37" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I38" t="n">
         <v>5.67</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="K38" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I39" t="n">
         <v>6.25</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K39" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I40" t="n">
         <v>6.72</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K40" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I41" t="n">
         <v>7.26</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K41" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I42" t="n">
         <v>7.41</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K42" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I43" t="n">
         <v>7.87</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K43" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I44" t="n">
         <v>7.65</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K44" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I45" t="n">
         <v>7.48</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K45" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I46" t="n">
         <v>7.45</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K46" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I47" t="n">
         <v>6.81</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K47" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I48" t="n">
         <v>6.46</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K48" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I49" t="n">
         <v>5.69</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K49" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I50" t="n">
         <v>4.399999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K50" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I51" t="n">
         <v>3.6</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K51" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I52" t="n">
         <v>3.53</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K52" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I53" t="n">
         <v>4.58</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K53" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I54" t="n">
         <v>6.17</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K54" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I55" t="n">
         <v>6.84</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K55" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I56" t="n">
         <v>6.779999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="K56" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I57" t="n">
         <v>6.41</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K57" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I58" t="n">
         <v>5.989999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K58" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I59" t="n">
         <v>6.52</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I60" t="n">
         <v>6.600000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K60" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I61" t="n">
         <v>6.58</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K61" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I62" t="n">
         <v>6.75</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K62" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I63" t="n">
         <v>6.98</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K63" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I64" t="n">
         <v>7.85</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="K64" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I65" t="n">
         <v>7.87</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K65" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I66" t="n">
         <v>7.510000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="K66" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I67" t="n">
         <v>7.260000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K67" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I68" t="n">
         <v>6.279999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="K68" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I69" t="n">
         <v>6.47</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K69" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I70" t="n">
         <v>6.87</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K70" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I71" t="n">
         <v>14.18</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K71" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I72" t="n">
         <v>14.39</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="K72" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46244</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I73" t="n">
         <v>14.18</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46244</v>
       </c>
       <c r="K73" t="n">
@@ -10522,57 +10534,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40060</v>
       </c>
       <c r="C2" t="n">
@@ -10602,10 +10614,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10635,10 +10647,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C4" t="n">
@@ -10672,10 +10684,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C5" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C6" t="n">
@@ -10746,10 +10758,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10820,10 +10832,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C9" t="n">
@@ -10857,10 +10869,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C10" t="n">
@@ -10894,10 +10906,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C11" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C12" t="n">
@@ -10968,10 +10980,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C13" t="n">
@@ -11005,10 +11017,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C14" t="n">
@@ -11042,10 +11054,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C15" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C16" t="n">
@@ -11116,10 +11128,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C17" t="n">
@@ -11153,10 +11165,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C18" t="n">
@@ -11190,10 +11202,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C19" t="n">
@@ -11227,10 +11239,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C20" t="n">
@@ -11264,10 +11276,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C21" t="n">
@@ -11301,10 +11313,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C22" t="n">
@@ -11338,10 +11350,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="C23" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C24" t="n">
@@ -11412,10 +11424,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C25" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C26" t="n">
@@ -11486,10 +11498,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C27" t="n">
@@ -11523,10 +11535,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C28" t="n">
@@ -11560,10 +11572,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C29" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C30" t="n">
@@ -11634,10 +11646,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C31" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C32" t="n">
@@ -11708,10 +11720,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C33" t="n">
@@ -11745,10 +11757,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C34" t="n">
@@ -11782,10 +11794,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C35" t="n">
@@ -11819,10 +11831,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C36" t="n">
@@ -11856,10 +11868,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C37" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="C38" t="n">
@@ -11930,10 +11942,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C39" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C40" t="n">
@@ -12004,10 +12016,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C41" t="n">
@@ -12041,10 +12053,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C42" t="n">
@@ -12078,10 +12090,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C43" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C44" t="n">
@@ -12152,10 +12164,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C45" t="n">
@@ -12189,10 +12201,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C46" t="n">
@@ -12226,10 +12238,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C47" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43962</v>
       </c>
       <c r="C48" t="n">
@@ -12300,10 +12312,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44053</v>
       </c>
       <c r="C49" t="n">
@@ -12337,10 +12349,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44144</v>
       </c>
       <c r="C50" t="n">
@@ -12374,10 +12386,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C51" t="n">
@@ -12411,10 +12423,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44326</v>
       </c>
       <c r="C52" t="n">
@@ -12448,10 +12460,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C53" t="n">
@@ -12485,10 +12497,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C54" t="n">
@@ -12522,10 +12534,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C55" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C56" t="n">
@@ -12596,10 +12608,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C57" t="n">
@@ -12633,10 +12645,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C58" t="n">
@@ -12670,10 +12682,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C59" t="n">
@@ -12707,10 +12719,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C60" t="n">
@@ -12744,10 +12756,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C61" t="n">
@@ -12781,10 +12793,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="C62" t="n">
@@ -12818,10 +12830,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C63" t="n">
@@ -12855,10 +12867,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C64" t="n">
@@ -12892,10 +12904,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C65" t="n">
@@ -12929,10 +12941,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C66" t="n">
@@ -12966,10 +12978,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C67" t="n">
@@ -13003,10 +13015,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C68" t="n">
@@ -13040,10 +13052,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C69" t="n">
@@ -13077,10 +13089,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C70" t="n">
@@ -13114,10 +13126,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C71" t="n">
@@ -13151,10 +13163,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="C72" t="n">
@@ -13188,10 +13200,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C73" t="n">
@@ -13225,10 +13237,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="C74" t="n">
@@ -13262,10 +13274,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C75" t="n">
@@ -13299,10 +13311,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C76" t="n">
@@ -13336,10 +13348,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C77" t="n">
@@ -13373,10 +13385,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C78" t="n">
@@ -13410,10 +13422,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="2" t="n">
         <v>46244</v>
       </c>
       <c r="C79" t="n">
@@ -13465,12 +13477,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/SPG.xlsx
+++ b/salidas/empresas/SPG.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>32.23006820678711</v>
+        <v>32.23005676269531</v>
       </c>
       <c r="C2" t="n">
         <v>76.88736724853516</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>32.58512115478516</v>
+        <v>32.58510971069336</v>
       </c>
       <c r="C3" t="n">
         <v>77.00803375244141</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>33.04462051391602</v>
+        <v>33.04459762573242</v>
       </c>
       <c r="C4" t="n">
         <v>78.09395599365234</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.57182693481445</v>
+        <v>31.57180023193359</v>
       </c>
       <c r="C6" t="n">
         <v>73.90803527832031</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>32.88417816162109</v>
+        <v>32.88417434692383</v>
       </c>
       <c r="C7" t="n">
         <v>76.98018646240234</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>33.91104888916016</v>
+        <v>33.91106414794922</v>
       </c>
       <c r="C8" t="n">
         <v>79.38407897949219</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>33.92840576171875</v>
+        <v>33.92840194702148</v>
       </c>
       <c r="C9" t="n">
         <v>78.69725036621094</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>36.26126098632812</v>
+        <v>36.26127624511719</v>
       </c>
       <c r="C10" t="n">
         <v>84.10832214355469</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>38.85419845581055</v>
+        <v>38.85420608520508</v>
       </c>
       <c r="C11" t="n">
         <v>90.12268829345703</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>41.13555526733398</v>
+        <v>41.13554382324219</v>
       </c>
       <c r="C12" t="n">
         <v>94.65203094482422</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.85723495483398</v>
+        <v>40.85721588134766</v>
       </c>
       <c r="C13" t="n">
         <v>94.01161193847656</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>46.14137268066406</v>
+        <v>46.14138031005859</v>
       </c>
       <c r="C14" t="n">
         <v>106.1702880859375</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>45.8012580871582</v>
+        <v>45.80123901367188</v>
       </c>
       <c r="C15" t="n">
         <v>104.6388473510742</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>45.19589996337891</v>
+        <v>45.1959228515625</v>
       </c>
       <c r="C16" t="n">
         <v>103.2559127807617</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>46.8331413269043</v>
+        <v>46.83312606811523</v>
       </c>
       <c r="C17" t="n">
         <v>106.9963302612305</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>44.20113754272461</v>
+        <v>44.20115661621094</v>
       </c>
       <c r="C18" t="n">
         <v>100.2208862304688</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>38.08552932739258</v>
+        <v>38.08552169799805</v>
       </c>
       <c r="C19" t="n">
         <v>86.35443115234375</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>35.42068862915039</v>
+        <v>35.42068481445312</v>
       </c>
       <c r="C20" t="n">
         <v>80.31221771240234</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>39.22543334960938</v>
+        <v>39.22542953491211</v>
       </c>
       <c r="C21" t="n">
         <v>88.09934234619141</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>43.11410522460938</v>
+        <v>43.11408233642578</v>
       </c>
       <c r="C23" t="n">
         <v>96.83316802978516</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>41.03200149536133</v>
+        <v>41.03199768066406</v>
       </c>
       <c r="C24" t="n">
         <v>91.37568664550781</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>36.20151519775391</v>
+        <v>36.20151138305664</v>
       </c>
       <c r="C25" t="n">
         <v>80.61850738525391</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>39.13223266601562</v>
+        <v>39.13220977783203</v>
       </c>
       <c r="C28" t="n">
         <v>86.23377227783203</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>42.05944061279297</v>
+        <v>42.0594596862793</v>
       </c>
       <c r="C29" t="n">
         <v>92.68436431884766</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>42.22591018676758</v>
+        <v>42.22589111328125</v>
       </c>
       <c r="C30" t="n">
         <v>92.22029876708984</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>39.36577224731445</v>
+        <v>39.36576461791992</v>
       </c>
       <c r="C32" t="n">
         <v>85.97389221191406</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>40.69623184204102</v>
+        <v>40.69621276855469</v>
       </c>
       <c r="C33" t="n">
         <v>88.06221771240234</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>41.60553741455078</v>
+        <v>41.60553359985352</v>
       </c>
       <c r="C34" t="n">
         <v>90.02987670898438</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.75070381164551</v>
+        <v>28.75071144104004</v>
       </c>
       <c r="C35" t="n">
         <v>62.21342849731445</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.69196128845215</v>
+        <v>20.69196319580078</v>
       </c>
       <c r="C36" t="n">
         <v>44.08679580688477</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>23.14450836181641</v>
+        <v>23.14450073242188</v>
       </c>
       <c r="C37" t="n">
         <v>49.31224060058594</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>18.72296333312988</v>
+        <v>18.72296524047852</v>
       </c>
       <c r="C38" t="n">
         <v>39.8915901184082</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.70139503479004</v>
+        <v>14.70139026641846</v>
       </c>
       <c r="C39" t="n">
         <v>30.72153472900391</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.3853816986084</v>
+        <v>15.38538265228271</v>
       </c>
       <c r="C40" t="n">
         <v>32.15087509155273</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>22.91817665100098</v>
+        <v>22.91818046569824</v>
       </c>
       <c r="C41" t="n">
         <v>47.89218139648438</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>24.02606964111328</v>
+        <v>24.02607536315918</v>
       </c>
       <c r="C42" t="n">
         <v>49.6278076171875</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>23.10940933227539</v>
+        <v>23.10942459106445</v>
       </c>
       <c r="C43" t="n">
         <v>47.73439788818359</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>28.84803009033203</v>
+        <v>28.8480396270752</v>
       </c>
       <c r="C45" t="n">
         <v>59.47479248046875</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>30.78423118591309</v>
+        <v>30.78423881530762</v>
       </c>
       <c r="C47" t="n">
         <v>63.46657562255859</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>33.20993041992188</v>
+        <v>33.20992660522461</v>
       </c>
       <c r="C48" t="n">
         <v>68.35371398925781</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>32.90826416015625</v>
+        <v>32.90824890136719</v>
       </c>
       <c r="C50" t="n">
         <v>67.73283386230469</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>36.09133148193359</v>
+        <v>36.09132766723633</v>
       </c>
       <c r="C51" t="n">
         <v>73.65004730224609</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>38.67750549316406</v>
+        <v>38.67751312255859</v>
       </c>
       <c r="C52" t="n">
         <v>78.92756652832031</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>41.03780364990234</v>
+        <v>41.03780746459961</v>
       </c>
       <c r="C53" t="n">
         <v>83.74411773681641</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>39.45969772338867</v>
+        <v>39.4597053527832</v>
       </c>
       <c r="C54" t="n">
         <v>79.99059295654297</v>
@@ -1578,7 +1578,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>41.40415573120117</v>
+        <v>41.40415191650391</v>
       </c>
       <c r="C56" t="n">
         <v>83.93226623535156</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>42.25783920288086</v>
+        <v>42.25784301757812</v>
       </c>
       <c r="C57" t="n">
         <v>85.08937072753906</v>
@@ -1622,7 +1622,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>43.32771682739258</v>
+        <v>43.32770538330078</v>
       </c>
       <c r="C58" t="n">
         <v>87.24365234375</v>
@@ -1647,7 +1647,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>44.86011123657227</v>
+        <v>44.8601188659668</v>
       </c>
       <c r="C59" t="n">
         <v>90.32925415039062</v>
@@ -1672,7 +1672,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>46.3845100402832</v>
+        <v>46.38449478149414</v>
       </c>
       <c r="C60" t="n">
         <v>92.66227722167969</v>
@@ -1697,7 +1697,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>46.85070419311523</v>
+        <v>46.85068511962891</v>
       </c>
       <c r="C61" t="n">
         <v>93.59360504150391</v>
@@ -1722,7 +1722,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>47.77366256713867</v>
+        <v>47.77366638183594</v>
       </c>
       <c r="C62" t="n">
         <v>95.43743896484375</v>
@@ -1747,7 +1747,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>52.21187591552734</v>
+        <v>52.21186828613281</v>
       </c>
       <c r="C63" t="n">
         <v>103.5183410644531</v>
@@ -1776,7 +1776,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>50.84537887573242</v>
+        <v>50.84535217285156</v>
       </c>
       <c r="C64" t="n">
         <v>100.8090286254883</v>
@@ -1805,7 +1805,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>54.34703063964844</v>
+        <v>54.34704971313477</v>
       </c>
       <c r="C65" t="n">
         <v>107.7516479492188</v>
@@ -1834,7 +1834,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>56.40302276611328</v>
+        <v>56.40303802490234</v>
       </c>
       <c r="C66" t="n">
         <v>111.0630264282227</v>
@@ -1863,7 +1863,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>55.52872467041016</v>
+        <v>55.52875518798828</v>
       </c>
       <c r="C67" t="n">
         <v>109.3414840698242</v>
@@ -1892,7 +1892,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>57.57350158691406</v>
+        <v>57.5734977722168</v>
       </c>
       <c r="C68" t="n">
         <v>113.3678283691406</v>
@@ -1921,7 +1921,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>56.53128814697266</v>
+        <v>56.53130340576172</v>
       </c>
       <c r="C69" t="n">
         <v>110.5362167358398</v>
@@ -1979,7 +1979,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>61.79473114013672</v>
+        <v>61.79472351074219</v>
       </c>
       <c r="C71" t="n">
         <v>120.8278427124023</v>
@@ -2008,7 +2008,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>60.24585723876953</v>
+        <v>60.24586486816406</v>
       </c>
       <c r="C72" t="n">
         <v>116.9708404541016</v>
@@ -2037,7 +2037,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>62.57849502563477</v>
+        <v>62.57849884033203</v>
       </c>
       <c r="C73" t="n">
         <v>121.298210144043</v>
@@ -2066,7 +2066,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>65.93698120117188</v>
+        <v>65.93695831298828</v>
       </c>
       <c r="C74" t="n">
         <v>127.8080902099609</v>
@@ -2095,7 +2095,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>66.21250152587891</v>
+        <v>66.21249389648438</v>
       </c>
       <c r="C75" t="n">
         <v>127.4506072998047</v>
@@ -2124,7 +2124,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>71.19746398925781</v>
+        <v>71.19750213623047</v>
       </c>
       <c r="C76" t="n">
         <v>137.0460968017578</v>
@@ -2153,7 +2153,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>76.04564666748047</v>
+        <v>76.04563903808594</v>
       </c>
       <c r="C77" t="n">
         <v>146.378173828125</v>
@@ -2182,7 +2182,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>72.5665283203125</v>
+        <v>72.56655883789062</v>
       </c>
       <c r="C78" t="n">
         <v>138.7770385742188</v>
@@ -2211,7 +2211,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>76.57072448730469</v>
+        <v>76.57070159912109</v>
       </c>
       <c r="C79" t="n">
         <v>146.4346160888672</v>
@@ -2240,7 +2240,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>78.94662475585938</v>
+        <v>78.94661712646484</v>
       </c>
       <c r="C80" t="n">
         <v>150.9783630371094</v>
@@ -2298,7 +2298,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>75.17790985107422</v>
+        <v>75.17788696289062</v>
       </c>
       <c r="C82" t="n">
         <v>142.8127899169922</v>
@@ -2327,7 +2327,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>75.37596130371094</v>
+        <v>75.37593841552734</v>
       </c>
       <c r="C83" t="n">
         <v>143.1890869140625</v>
@@ -2356,7 +2356,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>75.88619995117188</v>
+        <v>75.88621520996094</v>
       </c>
       <c r="C84" t="n">
         <v>143.1138305664062</v>
@@ -2414,7 +2414,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>79.90175628662109</v>
+        <v>79.90174865722656</v>
       </c>
       <c r="C86" t="n">
         <v>150.6867370605469</v>
@@ -2443,7 +2443,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>79.80461120605469</v>
+        <v>79.80461883544922</v>
       </c>
       <c r="C87" t="n">
         <v>149.4449615478516</v>
@@ -2472,7 +2472,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>79.65390777587891</v>
+        <v>79.65387725830078</v>
       </c>
       <c r="C88" t="n">
         <v>149.1627502441406</v>
@@ -2501,7 +2501,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>89.45487213134766</v>
+        <v>89.45494842529297</v>
       </c>
       <c r="C89" t="n">
         <v>167.5164642333984</v>
@@ -2530,7 +2530,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>84.15244293212891</v>
+        <v>84.15242767333984</v>
       </c>
       <c r="C90" t="n">
         <v>156.5757293701172</v>
@@ -2588,7 +2588,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>80.92669677734375</v>
+        <v>80.92668914794922</v>
       </c>
       <c r="C92" t="n">
         <v>150.5738525390625</v>
@@ -2617,7 +2617,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>74.18053436279297</v>
+        <v>74.1805419921875</v>
       </c>
       <c r="C93" t="n">
         <v>136.9990539550781</v>
@@ -2646,7 +2646,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>75.5048828125</v>
+        <v>75.50492095947266</v>
       </c>
       <c r="C94" t="n">
         <v>139.4449615478516</v>
@@ -2675,7 +2675,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>78.72417449951172</v>
+        <v>78.72416687011719</v>
       </c>
       <c r="C95" t="n">
         <v>145.3904113769531</v>
@@ -2704,7 +2704,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>76.94651031494141</v>
+        <v>76.94652557373047</v>
       </c>
       <c r="C96" t="n">
         <v>140.9689636230469</v>
@@ -2733,7 +2733,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>78.13265991210938</v>
+        <v>78.13264465332031</v>
       </c>
       <c r="C97" t="n">
         <v>143.1420440673828</v>
@@ -2762,7 +2762,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>79.5087890625</v>
+        <v>79.50881195068359</v>
       </c>
       <c r="C98" t="n">
         <v>145.6632232666016</v>
@@ -2791,7 +2791,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>83.47624206542969</v>
+        <v>83.47624969482422</v>
       </c>
       <c r="C99" t="n">
         <v>151.73095703125</v>
@@ -2849,7 +2849,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>89.64034271240234</v>
+        <v>89.64032745361328</v>
       </c>
       <c r="C101" t="n">
         <v>162.9350891113281</v>
@@ -2878,7 +2878,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>92.26658630371094</v>
+        <v>92.26661682128906</v>
       </c>
       <c r="C102" t="n">
         <v>166.4600067138672</v>
@@ -2907,7 +2907,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>92.16686248779297</v>
+        <v>92.16680908203125</v>
       </c>
       <c r="C103" t="n">
         <v>166.2799987792969</v>
@@ -2936,7 +2936,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>93.22550964355469</v>
+        <v>93.22552490234375</v>
       </c>
       <c r="C104" t="n">
         <v>168.1900024414062</v>
@@ -2965,7 +2965,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>94.98421478271484</v>
+        <v>94.98423004150391</v>
       </c>
       <c r="C105" t="n">
         <v>170.0299987792969</v>
@@ -2994,7 +2994,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>91.85029602050781</v>
+        <v>91.85030364990234</v>
       </c>
       <c r="C106" t="n">
         <v>164.4199981689453</v>
@@ -3023,7 +3023,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>100.1124649047852</v>
+        <v>100.1124267578125</v>
       </c>
       <c r="C107" t="n">
         <v>179.2100067138672</v>
@@ -3052,7 +3052,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>101.7329254150391</v>
+        <v>101.7329406738281</v>
       </c>
       <c r="C108" t="n">
         <v>180.8000030517578</v>
@@ -3081,7 +3081,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>102.4700622558594</v>
+        <v>102.4700775146484</v>
       </c>
       <c r="C109" t="n">
         <v>182.1100006103516</v>
@@ -3110,7 +3110,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>111.7824172973633</v>
+        <v>111.7824478149414</v>
       </c>
       <c r="C110" t="n">
         <v>198.6600036621094</v>
@@ -3139,7 +3139,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>107.8877716064453</v>
+        <v>107.8877563476562</v>
       </c>
       <c r="C111" t="n">
         <v>190.3600006103516</v>
@@ -3168,7 +3168,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>110.8802337646484</v>
+        <v>110.8801956176758</v>
       </c>
       <c r="C112" t="n">
         <v>195.6399993896484</v>
@@ -3197,7 +3197,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>102.8606491088867</v>
+        <v>102.8606185913086</v>
       </c>
       <c r="C113" t="n">
         <v>181.4900054931641</v>
@@ -3226,7 +3226,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>103.6526565551758</v>
+        <v>103.6526336669922</v>
       </c>
       <c r="C114" t="n">
         <v>181.3999938964844</v>
@@ -3284,7 +3284,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>106.9782485961914</v>
+        <v>106.9782257080078</v>
       </c>
       <c r="C116" t="n">
         <v>187.2200012207031</v>
@@ -3313,7 +3313,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>103.297966003418</v>
+        <v>103.2979965209961</v>
       </c>
       <c r="C117" t="n">
         <v>179.3200073242188</v>
@@ -3371,7 +3371,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>116.0518112182617</v>
+        <v>116.0517501831055</v>
       </c>
       <c r="C119" t="n">
         <v>201.4600067138672</v>
@@ -3429,7 +3429,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>112.9414901733398</v>
+        <v>112.9414749145508</v>
       </c>
       <c r="C121" t="n">
         <v>194.4400024414062</v>
@@ -3458,7 +3458,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>108.2016677856445</v>
+        <v>108.2017135620117</v>
       </c>
       <c r="C122" t="n">
         <v>186.2799987792969</v>
@@ -3487,7 +3487,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>111.2000198364258</v>
+        <v>111.1999969482422</v>
       </c>
       <c r="C123" t="n">
         <v>189.7299957275391</v>
@@ -3516,7 +3516,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>121.7262878417969</v>
+        <v>121.7263031005859</v>
       </c>
       <c r="C124" t="n">
         <v>207.6900024414062</v>
@@ -3545,7 +3545,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>117.904914855957</v>
+        <v>117.9049530029297</v>
       </c>
       <c r="C125" t="n">
         <v>201.1699981689453</v>
@@ -3574,7 +3574,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>116.7515106201172</v>
+        <v>116.7515487670898</v>
       </c>
       <c r="C126" t="n">
         <v>197.6399993896484</v>
@@ -3603,7 +3603,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>128.1289672851562</v>
+        <v>128.1289215087891</v>
       </c>
       <c r="C127" t="n">
         <v>216.8999938964844</v>
@@ -3661,7 +3661,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>128.2676086425781</v>
+        <v>128.2676696777344</v>
       </c>
       <c r="C129" t="n">
         <v>215.4700012207031</v>
@@ -3690,7 +3690,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>123.2314376831055</v>
+        <v>123.2314758300781</v>
       </c>
       <c r="C130" t="n">
         <v>207.0099945068359</v>
@@ -3719,7 +3719,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>110.7005386352539</v>
+        <v>110.7005310058594</v>
       </c>
       <c r="C131" t="n">
         <v>185.9600067138672</v>
@@ -3748,7 +3748,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>107.9193344116211</v>
+        <v>107.9193496704102</v>
       </c>
       <c r="C132" t="n">
         <v>179.6499938964844</v>
@@ -3777,7 +3777,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>106.7299118041992</v>
+        <v>106.7299346923828</v>
       </c>
       <c r="C133" t="n">
         <v>177.6699981689453</v>
@@ -3806,7 +3806,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>110.3943557739258</v>
+        <v>110.3943252563477</v>
       </c>
       <c r="C134" t="n">
         <v>183.7700042724609</v>
@@ -3893,7 +3893,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>100.2388687133789</v>
+        <v>100.2388763427734</v>
       </c>
       <c r="C137" t="n">
         <v>165.2599945068359</v>
@@ -3922,7 +3922,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>94.61209106445312</v>
+        <v>94.61212158203125</v>
       </c>
       <c r="C138" t="n">
         <v>154.25</v>
@@ -3951,7 +3951,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>99.21852874755859</v>
+        <v>99.21855163574219</v>
       </c>
       <c r="C139" t="n">
         <v>161.7599945068359</v>
@@ -4009,7 +4009,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>97.29921722412109</v>
+        <v>97.29917144775391</v>
       </c>
       <c r="C141" t="n">
         <v>156.8500061035156</v>
@@ -4038,7 +4038,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>99.87977600097656</v>
+        <v>99.87974548339844</v>
       </c>
       <c r="C142" t="n">
         <v>161.0099945068359</v>
@@ -4067,7 +4067,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>96.35626983642578</v>
+        <v>96.35627746582031</v>
       </c>
       <c r="C143" t="n">
         <v>155.3300018310547</v>
@@ -4096,7 +4096,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>101.5087356567383</v>
+        <v>101.5087738037109</v>
       </c>
       <c r="C144" t="n">
         <v>161.75</v>
@@ -4125,7 +4125,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>107.7781448364258</v>
+        <v>107.7781677246094</v>
       </c>
       <c r="C145" t="n">
         <v>171.7400054931641</v>
@@ -4154,7 +4154,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>102.5254516601562</v>
+        <v>102.5254592895508</v>
       </c>
       <c r="C146" t="n">
         <v>163.3699951171875</v>
@@ -4183,7 +4183,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>97.55076599121094</v>
+        <v>97.55077362060547</v>
       </c>
       <c r="C147" t="n">
         <v>153.5099945068359</v>
@@ -4212,7 +4212,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>98.08460235595703</v>
+        <v>98.08456420898438</v>
       </c>
       <c r="C148" t="n">
         <v>154.3500061035156</v>
@@ -4270,7 +4270,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>103.1149673461914</v>
+        <v>103.1149749755859</v>
       </c>
       <c r="C150" t="n">
         <v>160.2200012207031</v>
@@ -4299,7 +4299,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>109.5315246582031</v>
+        <v>109.5315093994141</v>
       </c>
       <c r="C151" t="n">
         <v>170.1900024414062</v>
@@ -4357,7 +4357,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>119.1402587890625</v>
+        <v>119.1402893066406</v>
       </c>
       <c r="C153" t="n">
         <v>183.0299987792969</v>
@@ -4386,7 +4386,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>115.0524063110352</v>
+        <v>115.0523986816406</v>
       </c>
       <c r="C154" t="n">
         <v>176.75</v>
@@ -4415,7 +4415,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>119.4592437744141</v>
+        <v>119.4592361450195</v>
       </c>
       <c r="C155" t="n">
         <v>183.5200042724609</v>
@@ -4444,7 +4444,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>122.1756591796875</v>
+        <v>122.1756439208984</v>
       </c>
       <c r="C156" t="n">
         <v>185.6900024414062</v>
@@ -4473,7 +4473,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>110.5298385620117</v>
+        <v>110.5298156738281</v>
       </c>
       <c r="C157" t="n">
         <v>167.9900054931641</v>
@@ -4502,7 +4502,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>119.8267211914062</v>
+        <v>119.8267822265625</v>
       </c>
       <c r="C158" t="n">
         <v>182.1199951171875</v>
@@ -4531,7 +4531,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>120.5336532592773</v>
+        <v>120.5336380004883</v>
       </c>
       <c r="C159" t="n">
         <v>181.1600036621094</v>
@@ -4560,7 +4560,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>121.2322692871094</v>
+        <v>121.2322540283203</v>
       </c>
       <c r="C160" t="n">
         <v>182.2100067138672</v>
@@ -4589,7 +4589,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>115.5701675415039</v>
+        <v>115.5701599121094</v>
       </c>
       <c r="C161" t="n">
         <v>173.6999969482422</v>
@@ -4618,7 +4618,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>109.1092224121094</v>
+        <v>109.109245300293</v>
       </c>
       <c r="C162" t="n">
         <v>162.0899963378906</v>
@@ -4647,7 +4647,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>107.5408096313477</v>
+        <v>107.5408248901367</v>
       </c>
       <c r="C163" t="n">
         <v>159.7599945068359</v>
@@ -4734,7 +4734,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>106.240852355957</v>
+        <v>106.2408676147461</v>
       </c>
       <c r="C166" t="n">
         <v>155.6499938964844</v>
@@ -4763,7 +4763,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>102.8485412597656</v>
+        <v>102.8485260009766</v>
       </c>
       <c r="C167" t="n">
         <v>150.6799926757812</v>
@@ -4792,7 +4792,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>104.6339721679688</v>
+        <v>104.6339874267578</v>
       </c>
       <c r="C168" t="n">
         <v>151.2100067138672</v>
@@ -4821,7 +4821,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>103.0770111083984</v>
+        <v>103.077033996582</v>
       </c>
       <c r="C169" t="n">
         <v>148.9600067138672</v>
@@ -4850,7 +4850,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>92.13682556152344</v>
+        <v>92.1368408203125</v>
       </c>
       <c r="C170" t="n">
         <v>133.1499938964844</v>
@@ -4879,7 +4879,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>86.47345733642578</v>
+        <v>86.47347259521484</v>
       </c>
       <c r="C171" t="n">
         <v>123.0800018310547</v>
@@ -4908,7 +4908,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>38.54351043701172</v>
+        <v>38.54350662231445</v>
       </c>
       <c r="C172" t="n">
         <v>54.86000061035156</v>
@@ -4937,7 +4937,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>46.91122055053711</v>
+        <v>46.91121673583984</v>
       </c>
       <c r="C173" t="n">
         <v>66.76999664306641</v>
@@ -4966,7 +4966,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>40.53883361816406</v>
+        <v>40.53882598876953</v>
       </c>
       <c r="C174" t="n">
         <v>57.70000076293945</v>
@@ -4995,7 +4995,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>48.04237747192383</v>
+        <v>48.04238510131836</v>
       </c>
       <c r="C175" t="n">
         <v>68.37999725341797</v>
@@ -5024,7 +5024,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>44.68996429443359</v>
+        <v>44.68996810913086</v>
       </c>
       <c r="C176" t="n">
         <v>62.34999847412109</v>
@@ -5107,7 +5107,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>45.8589973449707</v>
+        <v>45.85899353027344</v>
       </c>
       <c r="C179" t="n">
         <v>62.81000137329102</v>
@@ -5157,7 +5157,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>63.24695205688477</v>
+        <v>63.24692535400391</v>
       </c>
       <c r="C181" t="n">
         <v>85.27999877929688</v>
@@ -5182,7 +5182,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>68.92046356201172</v>
+        <v>68.92047882080078</v>
       </c>
       <c r="C182" t="n">
         <v>92.93000030517578</v>
@@ -5207,7 +5207,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>83.74583435058594</v>
+        <v>83.74584197998047</v>
       </c>
       <c r="C183" t="n">
         <v>112.9199981689453</v>
@@ -5232,7 +5232,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>84.376220703125</v>
+        <v>84.37623596191406</v>
       </c>
       <c r="C184" t="n">
         <v>113.7699966430664</v>
@@ -5282,7 +5282,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>96.36377716064453</v>
+        <v>96.36380004882812</v>
       </c>
       <c r="C186" t="n">
         <v>128.4900054931641</v>
@@ -5307,7 +5307,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>97.85621643066406</v>
+        <v>97.85620880126953</v>
       </c>
       <c r="C187" t="n">
         <v>130.4799957275391</v>
@@ -5332,7 +5332,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>95.91545104980469</v>
+        <v>95.91544342041016</v>
       </c>
       <c r="C188" t="n">
         <v>126.5199966430664</v>
@@ -5357,7 +5357,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>101.9272232055664</v>
+        <v>101.9272308349609</v>
       </c>
       <c r="C189" t="n">
         <v>134.4499969482422</v>
@@ -5382,7 +5382,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>99.64148712158203</v>
+        <v>99.64150238037109</v>
       </c>
       <c r="C190" t="n">
         <v>129.9700012207031</v>
@@ -5407,7 +5407,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>112.3755569458008</v>
+        <v>112.3755722045898</v>
       </c>
       <c r="C191" t="n">
         <v>146.5800018310547</v>
@@ -5432,7 +5432,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>117.1747817993164</v>
+        <v>117.1747970581055</v>
       </c>
       <c r="C192" t="n">
         <v>152.8399963378906</v>
@@ -5457,7 +5457,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>123.7848663330078</v>
+        <v>123.7848892211914</v>
       </c>
       <c r="C193" t="n">
         <v>159.7700042724609</v>
@@ -5482,7 +5482,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>114.0460205078125</v>
+        <v>114.0460433959961</v>
       </c>
       <c r="C194" t="n">
         <v>147.1999969482422</v>
@@ -5507,7 +5507,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>106.5772247314453</v>
+        <v>106.5772399902344</v>
       </c>
       <c r="C195" t="n">
         <v>137.5599975585938</v>
@@ -5536,7 +5536,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>103.2249298095703</v>
+        <v>103.2249450683594</v>
       </c>
       <c r="C196" t="n">
         <v>131.5599975585938</v>
@@ -5565,7 +5565,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>92.58544921875</v>
+        <v>92.58547210693359</v>
       </c>
       <c r="C197" t="n">
         <v>118</v>
@@ -5594,7 +5594,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>89.95699310302734</v>
+        <v>89.95697784423828</v>
       </c>
       <c r="C198" t="n">
         <v>114.6500015258789</v>
@@ -5652,7 +5652,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>86.55186462402344</v>
+        <v>86.55184173583984</v>
       </c>
       <c r="C200" t="n">
         <v>108.6399993896484</v>
@@ -5681,7 +5681,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>81.24594116210938</v>
+        <v>81.24593353271484</v>
       </c>
       <c r="C201" t="n">
         <v>101.9800033569336</v>
@@ -5710,7 +5710,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>72.73271942138672</v>
+        <v>72.73273468017578</v>
       </c>
       <c r="C202" t="n">
         <v>89.75</v>
@@ -5739,7 +5739,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>88.31656646728516</v>
+        <v>88.31657409667969</v>
       </c>
       <c r="C203" t="n">
         <v>108.9800033569336</v>
@@ -5768,7 +5768,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>96.79328155517578</v>
+        <v>96.79329681396484</v>
       </c>
       <c r="C204" t="n">
         <v>119.4400024414062</v>
@@ -5797,7 +5797,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>96.66648101806641</v>
+        <v>96.66647338867188</v>
       </c>
       <c r="C205" t="n">
         <v>117.4800033569336</v>
@@ -5826,7 +5826,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>105.7011947631836</v>
+        <v>105.7012023925781</v>
       </c>
       <c r="C206" t="n">
         <v>128.4600067138672</v>
@@ -5913,7 +5913,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>94.63773345947266</v>
+        <v>94.63772583007812</v>
       </c>
       <c r="C209" t="n">
         <v>113.3199996948242</v>
@@ -5942,7 +5942,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>87.81467437744141</v>
+        <v>87.81466674804688</v>
       </c>
       <c r="C210" t="n">
         <v>105.1500015258789</v>
@@ -5971,7 +5971,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>98.05115509033203</v>
+        <v>98.0511474609375</v>
       </c>
       <c r="C211" t="n">
         <v>115.4800033569336</v>
@@ -6000,7 +6000,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>105.7947158813477</v>
+        <v>105.7947082519531</v>
       </c>
       <c r="C212" t="n">
         <v>124.5999984741211</v>
@@ -6029,7 +6029,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>96.36149597167969</v>
+        <v>96.36150360107422</v>
       </c>
       <c r="C213" t="n">
         <v>113.4899978637695</v>
@@ -6116,7 +6116,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>107.8106231689453</v>
+        <v>107.8106307983398</v>
       </c>
       <c r="C216" t="n">
         <v>124.8899993896484</v>
@@ -6174,7 +6174,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>121.4054489135742</v>
+        <v>121.4054260253906</v>
       </c>
       <c r="C218" t="n">
         <v>138.6100006103516</v>
@@ -6203,7 +6203,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>129.7525177001953</v>
+        <v>129.7525482177734</v>
       </c>
       <c r="C219" t="n">
         <v>148.1399993896484</v>
@@ -6232,7 +6232,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>138.8435974121094</v>
+        <v>138.8436126708984</v>
       </c>
       <c r="C220" t="n">
         <v>156.4900054931641</v>
@@ -6261,7 +6261,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>124.6833038330078</v>
+        <v>124.6833114624023</v>
       </c>
       <c r="C221" t="n">
         <v>140.5299987792969</v>
@@ -6290,7 +6290,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>134.2477111816406</v>
+        <v>134.2477264404297</v>
       </c>
       <c r="C222" t="n">
         <v>151.3099975585938</v>
@@ -6319,7 +6319,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>136.4571838378906</v>
+        <v>136.4571685791016</v>
       </c>
       <c r="C223" t="n">
         <v>151.8000030517578</v>
@@ -6348,7 +6348,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>137.9314117431641</v>
+        <v>137.931396484375</v>
       </c>
       <c r="C224" t="n">
         <v>153.4400024414062</v>
@@ -6435,7 +6435,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>153.9450531005859</v>
+        <v>153.9450836181641</v>
       </c>
       <c r="C227" t="n">
         <v>169.1199951171875</v>
@@ -6493,7 +6493,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>158.5691375732422</v>
+        <v>158.5691223144531</v>
       </c>
       <c r="C229" t="n">
         <v>172.2100067138672</v>
@@ -6638,7 +6638,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>152.0189361572266</v>
+        <v>152.0189666748047</v>
       </c>
       <c r="C234" t="n">
         <v>163.0700073242188</v>
@@ -6667,7 +6667,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>151.8324432373047</v>
+        <v>151.8324737548828</v>
       </c>
       <c r="C235" t="n">
         <v>160.7599945068359</v>
@@ -6725,7 +6725,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>170.6273345947266</v>
+        <v>170.6273651123047</v>
       </c>
       <c r="C237" t="n">
         <v>180.6600036621094</v>
@@ -6783,7 +6783,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>167.9778137207031</v>
+        <v>167.9778289794922</v>
       </c>
       <c r="C239" t="n">
         <v>175.7599945068359</v>
@@ -6812,7 +6812,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>178.0702667236328</v>
+        <v>178.0702819824219</v>
       </c>
       <c r="C240" t="n">
         <v>186.3200073242188</v>
@@ -6899,7 +6899,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>197.2205810546875</v>
+        <v>197.2205963134766</v>
       </c>
       <c r="C243" t="n">
         <v>203.8500061035156</v>
